--- a/config/services.xlsx
+++ b/config/services.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -69,10 +69,10 @@
 每条之间加一行 ---</t>
   </si>
   <si>
-    <t>personal-dynamic-service-plus</t>
-  </si>
-  <si>
-    <t>pdynamic</t>
+    <t>member-vip-service-plus</t>
+  </si>
+  <si>
+    <t>vip-act</t>
   </si>
   <si>
     <t>cloud-test-default-group</t>
@@ -82,10 +82,13 @@
 kind: Deployment
 metadata:
   annotations:
-    deployment.kubernetes.io/revision: '96'
+    deployment.kubernetes.io/revision: '54'
+    objectset.rio.cattle.io/applied: H4sIAAAAAAAA/5xUUW/bNhD+LwfszZIlJXEcvQ0J2j20a7CsfRmC4USebTYUyR1PTrRA/30gY2dy12FrAQMWye8+3t338Z4Bg/lEHI130AKGEJf7GhbwYJyGFm4oWD/25AQW0JOgRkFonwGd84JivItp6bvPpCSSlGx8qVDEUmn80iSSjWoUNmtddE13VpxvVqtifbmqipXqVo06r5qrswamBVjsyGY6DKF02BO00Cvdq+JxZ4SKSLw3ioooyEJcCMWU179dvsO4gxbq9Xq1xrq7ulQXl/rsbENVs+oumkZfNt2V3tRVjVfNpksp/P9LEzIGVAmet6YFxEAqpR/Yb5livCHU1ji6I+WdjtCuqmoBTMEahRHaOi32JjX/JxPF8/jO9EagrasFRLKkxHMi7FHU7t13tWdKeQmj0HZMseytNW77MWgUeuF+uht4m8iaix+SzPj00eEejcXOHrenBcgY0uqXE4K0T32wR7KZRRRTNsivpqco2Ado3WDt9+o8zRqsvBM0jjhC+9szkNvn/wNVDGzctgzsN8ZSLFGJ2RMsYI92SIBRjwfOxWvQZ4xjkJKc4jGI5zJgjI+e9SzukwlN1Zz//ufjDe1hul+A6TF3rq7K+ir91ufLh3Vc/lc1bV1WcAi/Hay99daoEVr40T7iGOFbnMgU/cCKckdtMlD+UmFIieV323sec5ZvTVKM6Y+B4hxWlafAhMvScm9cVvE9xZiSRUlvaqlpv5ydFtZv4av4Y2FvjM0SeDv09N4PTl6069PnkdX67az2vEoSnWBI1NJ6hVZMT3+D06qY7zOh/uDsCK3wQNN9kku7eO3dxmzzzAqH8TVzjnFbS8WhPwWTD+TmLkncfpCZJ+r5MUp6DBJn52fzc6f9yWED0/2U03rt07UdohC/MZzFfXXIHSkmOck2IMZi5rxih9x5LmKGZn86r+luNkic5x5tKoQHerFCdtM//RfVjvRgiX9+uUzTBgcrxet+wpAa2Mh47Z3Qk0D7fOqZt4yKbomN17MReDTBSy07Hw/SPkM4SLxHXlrTLbVXD8RHVxzmz43hXM74ga/ThKHZ3H51zNdYvzTOgW8W/oWHpvtpmqa/AgAA///fnD3pIwcAAA
+    objectset.rio.cattle.io/id: fc2ca28d-b2b3-4f66-8760-6cb62c402932
   labels:
-    app.name: personal-dynamic-service-plus
-  name: personal-dynamic-service-plus
+    app.name: member-vip-test
+    objectset.rio.cattle.io/hash: 18868a1b97c57d33fe026b522d72b9df101a92fb
+  name: member-vip-test
   namespace: test
 spec:
   progressDeadlineSeconds: 600
@@ -93,7 +96,7 @@
   revisionHistoryLimit: 10
   selector:
     matchLabels:
-      app.name: personal-dynamic-service-plus
+      app.name: member-vip-test
   strategy:
     rollingUpdate:
       maxSurge: 25%
@@ -103,53 +106,26 @@
     metadata:
       creationTimestamp: null
       labels:
-        app.name: personal-dynamic-service-plus
+        app.name: member-vip-test
     spec:
       containers:
       - env:
-        - name: ACTIVE_PROFILE
-          value: test
-        envFrom:
-        - secretRef:
-            name: personal-dynamic-secret
-        image: d133ypcgtest01-c138372f.ecis.guangzhou-2.cmecloud.cn/k8s/personal-dynamic-service-plus:compatible.202512031708
+        - name: spring.profiles.active
+          value: ydy-test
+        - name: jasypt.encryptor.password
+          value: Vip2024_zwDev
+        image: 10.19.19.84/k8s/member-vip-test:202512181600
         imagePullPolicy: Always
-        livenessProbe:
-          failureThreshold: 10
-          httpGet:
-            path: /actuator/health/liveness
-            port: 8089
-            scheme: HTTP
-          periodSeconds: 10
-          successThreshold: 1
-          timeoutSeconds: 1
-        name: personal-dynamic-service-plus
-        readinessProbe:
-          failureThreshold: 3
-          httpGet:
-            path: /actuator/health/liveness
-            port: 8089
-            scheme: HTTP
-          initialDelaySeconds: 5
-          periodSeconds: 5
-          successThreshold: 1
-          timeoutSeconds: 1
+        name: member-vip-test
         resources:
           limits:
-            cpu: '1'
+            cpu: '8'
             memory: 10Gi
           requests:
-            cpu: 100m
-            memory: 1Gi
-        startupProbe:
-          failureThreshold: 50
-          httpGet:
-            path: /actuator/health/liveness
-            port: 8089
-            scheme: HTTP
-          periodSeconds: 10
-          successThreshold: 1
-          timeoutSeconds: 1
+            cpu: '1'
+            memory: 2Gi
+        securityContext:
+          privileged: true
         terminationMessagePath: /dev/termination-log
         terminationMessagePolicy: File
         volumeMounts:
@@ -169,7 +145,20 @@
           value: '2'
       dnsPolicy: ClusterFirst
       imagePullSecrets:
-      - name: paas-d133ypcgtest01-harbor-secret
+      - name: paas-10.19.19.84-harbor-secret
+      initContainers:
+      - command:
+        - sh
+        - -c
+        - sysctl -w net.core.somaxconn=10000 &amp;&amp; sysctl -w net.ipv4.tcp_max_syn_backlog=65535
+        image: busybox
+        imagePullPolicy: Always
+        name: sysctl-modifier
+        resources: {}
+        securityContext:
+          privileged: true
+        terminationMessagePath: /dev/termination-log
+        terminationMessagePolicy: File
       nodeSelector:
         normal: 'true'
       restartPolicy: Always
@@ -188,57 +177,55 @@
 </t>
   </si>
   <si>
-    <t>kind: Service
+    <t xml:space="preserve">kind: Service
 metadata:
-  annotations:
-    objectset.rio.cattle.io/applied: H4sIAAAAAAAA/5SRQWsbMRCF/8s7S+4mu5Z3dSuBQi7F0NJLyWFWmm3UypKQJgZj/N+LauitkB4lvnnfY+YKKuEb1xZygsX5AQq/QvKw+ML1HBxD4cRCnoRgr6CUspCEnFp/5vUnO2ksuxryzpFI5F3IH0JPmPbuYd6bWftlnvTk2euFjdEHYw6GHw9+mA1uCpFWjn/iqJRdohPDonBtOVHU/pLoFJxu9z66xLcG9U/zK7VXWIz70Sx+2Hvnhm0d/LqO0+Q3Zl7mdXLbuCw8P45D97/HqNvZ4Y62Qq7zwk36eCvsevlQPtEpxMAN9juej2eDF4WSq/SP6/s0Hcd9CnYZh0Gh1CzZ5QiLr09HKAjVHyzHv8jtRaFxZCe5/tcWe3lu/fYfty2kIBdYfM6pH10upQc8xbcmXJ+PuN1+BwAA//++RQUoLQIAAA
-    objectset.rio.cattle.io/id: 45c18568-d984-4ded-9e66-76676e27d086
+  annotations: {}
   labels:
-    app.name: personal-dynamic-service-plus
-    objectset.rio.cattle.io/hash: 35369d05dcc0fb0dbb344dfeee98b4cf399e8230
-  name: personal-dynamic-service-plus-svc
+    app.name: member-vip-test
+  name: member-vip-test-svc
   namespace: test
 spec:
-  clusterIP: fd11:1111:1111:15::cb5c
+  clusterIP: fd11:1111:1111:15::7261
   clusterIPs:
-  - fd11:1111:1111:15::cb5c
+  - fd11:1111:1111:15::7261
   ipFamilies:
   - IPv6
   ipFamilyPolicy: SingleStack
   ports:
-  - name: personal-dynamic-service-plus-port
-    port: 9300
+  - name: member-vip-test-port
+    port: 19005
     protocol: TCP
-    targetPort: 9300
+    targetPort: 19005
   selector:
-    app.name: personal-dynamic-service-plus
+    app.name: member-vip-test
   sessionAffinity: None
-  type: ClusterIP</t>
+  type: ClusterIP
+</t>
   </si>
   <si>
     <t xml:space="preserve">apiVersion: networking.k8s.io/v1
 kind: Ingress
 metadata:
   annotations:
-    objectset.rio.cattle.io/applied: H4sIAAAAAAAA/4yRsY7cIBCG32Vq4/OdvaxNmypNlCJKE6UYYPZM1gbEzG7utPK7R6yjdNGtRDFI/N/3AzfAHL5T4ZAiGIgkv1M5h/jankduQ3q6PkMD5xA9GPgcXwsxQwMrCXoUBHMDjDEJSkiR6zbZX+SESdoSUutQZKEKCpUwHNzzeNCj8tM4qMGTVxNprY5aHzW9HH03atgaWNDScsdhzm3ElcBApsIp4qL8e8Q1OMVUrsGRysullvqfeUaewUB/6PXku4N3rjvZzlvbD4M/EdE02sGd+mmi8aXvqv8Ro8IcOLzBfpozuhoRYqkEzuRq/7C/2acFmb/s1H+5clmIwfy4wZxYPvK1Fd26tEIDs0iu9Iwy7wSL7kz1l27wN1THh+7BVwcN5FTkHrmslgqYqe+6bduauwMMPME+fnvPFfm10Cm8wfZzq+tPAAAA//9yiA5rRwIAAA
-    objectset.rio.cattle.io/id: 45c18568-d984-4ded-9e66-76676e27d086
+    objectset.rio.cattle.io/applied: H4sIAAAAAAAA/3SQsY6dMBBF/2VqYEHAPnCbKk2UIkoTpZhnjxcHsC3PLNkV4t8jQ5Qm+ySEZN2554xmB4zuOyV2wYMCT/I7pNn5l2oeuHLhaWuggNl5Awo++5dEzFDASoIGBUHtgN4HQXHBc36G+y/SwiRVcqHSKLJQBrlM6NrGom5tSYRUdmNN5UB2LHF8tjUS2cYYOApY8E7LicMYK48rgYKV1julcnOxFGKB4qFrQp5AQdMNN2vbfhwHY0zdjh0Nt7ptNfad6bE2iDd6tn02fuwoMTp2b3DlHFHnodN+FMCRdN7RXXf5tCDzl4vzr5deF2JQP3aYAsv/hur86bBCAZNIzLyIMl2dO+qZ8u13YEqby/r90a68aSgghiTn0GtOQTVjXffHcRQnFhQ8/e2hFrc5eYcr+fYeM/RrIuve4Ph55O9PAAAA///f8j13HwIAAA
+    objectset.rio.cattle.io/id: 431fac3f-eeae-490e-8ef9-a96f0aeef1dd
   labels:
-    app.name: personal-dynamic-service-plus
-    objectset.rio.cattle.io/hash: 35369d05dcc0fb0dbb344dfeee98b4cf399e8230
-  name: personal-dynamic-service-plus-apisix
+    app.name: member-vip-test
+    objectset.rio.cattle.io/hash: 1487ff35998ddd0394e87033ca54d5a0daa7e6f5
+  name: member-vip-test-apisix
   namespace: test
 spec:
   ingressClassName: apisix
   rules:
-  - host: personal-dynamic-service-plus.test.com
+  - host: member-vip-test.test.com
     http:
       paths:
       - backend:
           service:
-            name: personal-dynamic-service-plus-svc
+            name: member-vip-test-svc
             port:
-              number: 9300
-        path: /
+              number: 19005
+        path: /member-activity
         pathType: Prefix
 </t>
   </si>
@@ -253,7 +240,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -281,13 +268,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -632,7 +612,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -652,21 +632,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFDEE0E3"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFDEE0E3"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFDEE0E3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -788,137 +753,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="8">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -931,20 +896,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1257,18 +1210,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="23.5454545454545" customWidth="1"/>
-    <col min="2" max="2" width="36.7272727272727" customWidth="1"/>
-    <col min="3" max="3" width="31.8181818181818" customWidth="1"/>
-    <col min="4" max="4" width="25.9090909090909" customWidth="1"/>
-    <col min="5" max="5" width="25.5454545454545" customWidth="1"/>
-    <col min="6" max="6" width="29.5454545454545" customWidth="1"/>
+    <col min="1" max="1" width="16.3611111111111" customWidth="1"/>
+    <col min="2" max="6" width="18.7314814814815" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" spans="1:6">
+    <row r="1" ht="16.8" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1312,13 +1261,13 @@
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -1327,38 +1276,6 @@
       <c r="F3" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" ht="17" spans="1:6">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" ht="17" spans="1:6">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" ht="17" spans="1:6">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1371,7 +1288,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1383,7 +1300,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
